--- a/AAII_Financials/Yearly/PB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PB_YR_FIN.xlsx
@@ -2972,10 +2972,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2162100</v>
+        <v>1960900</v>
       </c>
       <c r="E58" s="3">
-        <v>3422600</v>
+        <v>3200700</v>
       </c>
       <c r="F58" s="3">
         <v>3729100</v>
@@ -3074,10 +3074,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>30675500</v>
+        <v>30474300</v>
       </c>
       <c r="E60" s="3">
-        <v>31845900</v>
+        <v>31624000</v>
       </c>
       <c r="F60" s="3">
         <v>30943700</v>
@@ -3125,10 +3125,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18000</v>
+        <v>219300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>221900</v>
       </c>
       <c r="F61" s="3">
         <v>309300</v>
